--- a/extenbooks/XS1403.xlsx
+++ b/extenbooks/XS1403.xlsx
@@ -1313,7 +1313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1419,121 +1419,130 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Variable capital (W_p) = total wages paid to productive workers, in billions of current dollars. For each productive SIC division i: W_p^i = ec_p^i × L_p^i, where ec_p^i = 52 × (w_pn^i)_BLS × (EC^i / WS^i)_NIPA. The BLS weekly production worker wage is annualized (×52) and grossed up by the NIPA ratio of employee compensation to wages and salaries (to include employer contributions to superannuation and benefits). Total variable capital V* = sum over all productive sectors.</t>
+          <t>STUDY ANCHOR (Mohun 2005 Table 3, Services sector productive wages 1988, and eqs (5)-(7)). Total productive services wages 1988 ($ million): Benchmark 241,564; ST 409,098; SM 245,822. CITATION CORRECTION: prior research JSON and methodology_summary cited "Mohun 2005 Table 2, p.807" for this variable-capital series — that is WRONG: Table 2 is productive-labour HEADCOUNTS; the wages / variable-capital anchor is Table 3 (with eqs 5-7). NOTE: series XS1403-A is a whole-economy V* RECONSTRUCTION over 1948-1989 ($thousands: 1.11e6 in 1948 -&gt; 1.32e7 in 1989) and does NOT reproduce Mohun services-only 1988 Table 3 figure. No year-matched external anchor exists; the 1948 refval is the series own output (tautological), documented as a divergence.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mohun_2005, Section 2.2, Equations 5-6; full_transcription.md</t>
+          <t>Mohun 2005, Table 3 (Services sector productive wages 1988) + eqs (5)-(7), CJE 29(5):799-815 (Section 3.1.2, ~p.807)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>st_vs_sm_wage_comparison</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Figure 1 ST-to-SM ratio for productive wages W_p: 1964: ST = 107.6% of SM; 1989: ST = 120.8% of SM; 2001: ST = 124.1% of SM. The ST method substantially overestimates variable capital. The overestimate is primarily driven by the Services sector wage approximation, where ST assumes uniform wages across all Services divisions and across production/nonproduction workers — Mohun calls this a 'drastic assumption.' Figure 3 shows W_p/W: ST starts ~0.44 (1964), declines to ~0.32 (2001); SM starts ~0.41 (1964), declines to ~0.26 (2001).</t>
+          <t>Variable capital (W_p) = total wages paid to productive workers, in billions of current dollars. For each productive SIC division i: W_p^i = ec_p^i × L_p^i, where ec_p^i = 52 × (w_pn^i)_BLS × (EC^i / WS^i)_NIPA. The BLS weekly production worker wage is annualized (×52) and grossed up by the NIPA ratio of employee compensation to wages and salaries (to include employer contributions to superannuation and benefits). Total variable capital V* = sum over all productive sectors.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mohun_2005, Figs 1 and 3; full_transcription.md Section 4</t>
+          <t>Mohun_2005, Section 2.2, Equations 5-6; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>services_wage_approximation</t>
+          <t>st_vs_sm_wage_comparison</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Services sector wage performance 1988-2001 benchmark comparison: ST achieves 172% of benchmark (sd 3.71) — a 72% overestimate. SM achieves 101.5% of benchmark (sd 1.08) — a 1.5% overestimate. In the benchmark year 1988, ST services productive wages = $409,098 million vs benchmark $241,564 million. SM = $245,822 million. The SM method weights BLS aggregate Services production wages by the NIPA ratio of division compensation to average Services compensation: W_p^{s,j}_SM = 52 × w_pn^s_BLS × (EC^s/WS^s)_NIPA × (ec^{s,j}/ec^s)_NIPA × L_p^{s,j}_SM.</t>
+          <t>Figure 1 ST-to-SM ratio for productive wages W_p: 1964: ST = 107.6% of SM; 1989: ST = 120.8% of SM; 2001: ST = 124.1% of SM. The ST method substantially overestimates variable capital. The overestimate is primarily driven by the Services sector wage approximation, where ST assumes uniform wages across all Services divisions and across production/nonproduction workers — Mohun calls this a 'drastic assumption.' Figure 3 shows W_p/W: ST starts ~0.44 (1964), declines to ~0.32 (2001); SM starts ~0.41 (1964), declines to ~0.26 (2001).</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mohun_2005, Table 3; full_transcription.md Section 3.1.2</t>
+          <t>Mohun_2005, Figs 1 and 3; full_transcription.md Section 4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>transportation_wage_note</t>
+          <t>services_wage_approximation</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ST also overestimates Transportation and Public Utilities wages by using Class 1 Railroads (SIC 4011) as proxy for the entire division. By 2001 Class 1 Railroad employment was only 2.7% of division BLS employment (down from 31.7% in 1948). SM uses the division-wide BLS wage from 1964 onwards. ST overestimate: +2.3% (1964), +44% (1989), peak +50.6% (1997), +22.7% (2001).</t>
+          <t>Services sector wage performance 1988-2001 benchmark comparison: ST achieves 172% of benchmark (sd 3.71) — a 72% overestimate. SM achieves 101.5% of benchmark (sd 1.08) — a 1.5% overestimate. In the benchmark year 1988, ST services productive wages = $409,098 million vs benchmark $241,564 million. SM = $245,822 million. The SM method weights BLS aggregate Services production wages by the NIPA ratio of division compensation to average Services compensation: W_p^{s,j}_SM = 52 × w_pn^s_BLS × (EC^s/WS^s)_NIPA × (ec^{s,j}/ec^s)_NIPA × L_p^{s,j}_SM.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mohun_2005, Section 3.2; full_transcription.md</t>
+          <t>Mohun_2005, Table 3; full_transcription.md Section 3.1.2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>transportation_wage_note</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ST also overestimates Transportation and Public Utilities wages by using Class 1 Railroads (SIC 4011) as proxy for the entire division. By 2001 Class 1 Railroad employment was only 2.7% of division BLS employment (down from 31.7% in 1948). SM uses the division-wide BLS wage from 1964 onwards. ST overestimate: +2.3% (1964), +44% (1989), peak +50.6% (1997), +22.7% (2001).</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mohun_2005, Section 3.2; full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>impact_on_exploitation_rate</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>The overestimate of ST productive wages is partially attenuated by the ST underestimate of productive workers numbers. Net impact: ST variable capital overestimate flows through to a compressed exploitation rate. The variable capital share W_p/W is the key driver of the exploitation rate, since e = S/V = (Y - W_p)/W_p = (Y/W_p) - 1. A 24% overestimate of W_p in 2001 means ST reports systematically lower exploitation — confirmed by Fig 4 comparison showing ST e = 2.22 vs SM e = 3.00 in 2001.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Mohun_2005, Fig 4; full_transcription.md Section 4</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>methodology_summary</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Variable capital (wages of productive workers) under Mohun SM approximation, billions of current dollars. W_p/W declines from ~0.41 (1964) to ~0.26 (2001) under SM — steeper than ST's 0.44 to 0.32. ST overestimates by 7.6% (1964) to 24.1% (2001), primarily from services sector wage mis-approximation. Loaded from Mohun 2005 Table 2 via L15.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Variable capital (wages of productive workers) under Mohun SM approximation, billions of current dollars. W_p/W declines from ~0.41 (1964) to ~0.26 (2001) under SM — steeper than ST's 0.44 to 0.32. ST overestimates by 7.6% (1964) to 24.1% (2001), primarily from services sector wage mis-approximation. Data provenance: loaded (pass-through) from project reconstruction file Mohun_mohun_variable_capital_1948_1989_CORRECTED.csv col V_star_mohun (whole-economy V*, $thousands), a book-period 1948-1989 reconstruction — NOT Mohun 2005 Table 2 (the prior Table 2 citation was wrong; the concept anchor is Table 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Services wage approximation has no benchmark validation pre-1988</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1550,7 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Transportation and Public Utilities: Mohun's SM correction is large (up to 50.6% overestimate for ST); SM uses division-wide BLS wage</t>
+          <t>Services wage approximation has no benchmark validation pre-1988</t>
         </is>
       </c>
     </row>
@@ -1549,23 +1558,23 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Transportation and Public Utilities: Mohun's SM correction is large (up to 50.6% overestimate for ST); SM uses division-wide BLS wage</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Agriculture and Government Enterprises overestimates in ST have small net effect due to small sector weights</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>XS1401</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1582,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>XS1402</t>
+          <t>XS1401</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1590,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>XS1404</t>
+          <t>XS1402</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1598,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S507</t>
+          <t>XS1404</t>
         </is>
       </c>
     </row>
@@ -1597,37 +1606,45 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
+          <t>S507</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>S512</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mohun_2005</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
+          <t>citations:</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Mohun_2005</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1740,7 +1757,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[0, 15000]</t>
+          <t>[0, 15000000]</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS1403.xlsx
+++ b/extenbooks/XS1403.xlsx
@@ -1162,7 +1162,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>`data/source/external_studies/Mohun_mohun_variable_capital_1948_1989_CORRECTED.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_XS1403_variable_capital_mohun2005.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_XS1403_variable_capital_mohun2005.py`.</t>
+          <t>`data/source/external_studies/Mohun_mohun_variable_capital_1948_1989_CORRECTED.csv` (copied from predecessor-build's ExternalSources). Loader: `code/L01_loaders/L01_XS1403_variable_capital_mohun2005.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_XS1403_variable_capital_mohun2005.py`.</t>
         </is>
       </c>
     </row>
